--- a/Assets/LingBoCanteen/1_Datatables/Excel/Dish.xlsx
+++ b/Assets/LingBoCanteen/1_Datatables/Excel/Dish.xlsx
@@ -1,132 +1,684 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Game\GoldenDolphin\Assets\LingBoCanteen\1_Datatables\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B72947ED-58F0-4D23-AC42-C10884467B61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="18052" windowHeight="8655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="95">
   <si>
     <t>#</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>菜品配置表</t>
   </si>
   <si>
     <t>Id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AssetName</t>
+  </si>
+  <si>
+    <t>IngList</t>
+  </si>
+  <si>
+    <t>SeasoningList</t>
+  </si>
+  <si>
+    <t>PotList</t>
+  </si>
+  <si>
+    <t>EarnMoney</t>
   </si>
   <si>
     <t>int</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>菜品配置表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>list&lt;int&gt;</t>
   </si>
   <si>
     <t>菜品编号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>菜品名</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AssetName</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>资源名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>list&lt;int&gt;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>IngList</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>所需食材列表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>EarnMoney</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>所需调料列表</t>
+  </si>
+  <si>
+    <t>所需锅</t>
+  </si>
+  <si>
+    <t>需求抽取权重</t>
   </si>
   <si>
     <t>出售菜品可获金币</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SanChange</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>San值增减变化</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金纹南瓜浓汤</t>
+  </si>
+  <si>
+    <t>Dishes_PumpkinSoup</t>
+  </si>
+  <si>
+    <t>3001</t>
+  </si>
+  <si>
+    <t>4005</t>
+  </si>
+  <si>
+    <t>蘑菇滑鸡煲</t>
+  </si>
+  <si>
+    <t>Dishes_ChickenWithMushroom</t>
+  </si>
+  <si>
+    <t>3002,3018</t>
+  </si>
+  <si>
+    <t>柠檬雪葩</t>
+  </si>
+  <si>
+    <t>Dishes_LemonSorbet</t>
+  </si>
+  <si>
+    <t>3003</t>
+  </si>
+  <si>
+    <t>鱼汤</t>
+  </si>
+  <si>
+    <t>Dishes_FishSoup</t>
+  </si>
+  <si>
+    <t>3007,3019</t>
+  </si>
+  <si>
+    <t>4001,4004,4006</t>
+  </si>
+  <si>
+    <t>盐葱香煎牛肉</t>
+  </si>
+  <si>
+    <t>Dishes_BeefWithScallions</t>
+  </si>
+  <si>
+    <t>3004,3007,3017</t>
+  </si>
+  <si>
+    <t>牛排</t>
+  </si>
+  <si>
+    <t>Dishes_Steak</t>
+  </si>
+  <si>
+    <t>3002,3005,3017</t>
+  </si>
+  <si>
+    <t>柠檬虾滑</t>
+  </si>
+  <si>
+    <t>Dishes_LemonShrimpPaste</t>
+  </si>
+  <si>
+    <t>3003,3006,3007,3021</t>
+  </si>
+  <si>
+    <t>4002,4005</t>
+  </si>
+  <si>
+    <t>仰望星空派</t>
+  </si>
+  <si>
+    <t>Dishes_StargazyPie</t>
+  </si>
+  <si>
+    <t>3008,3019,3022</t>
+  </si>
+  <si>
+    <t>4002</t>
+  </si>
+  <si>
+    <t>石板烤肉</t>
+  </si>
+  <si>
+    <t>Dishes_StoneGrilledMeat</t>
+  </si>
+  <si>
+    <t>3006,3020</t>
+  </si>
+  <si>
+    <t>4002,4004</t>
+  </si>
+  <si>
+    <t>蒜泥青苹果鸡排</t>
+  </si>
+  <si>
+    <t>Dishes_AppleChickenCutlet</t>
+  </si>
+  <si>
+    <t>3004,3009,3018</t>
+  </si>
+  <si>
+    <t>4002,4004,4006</t>
+  </si>
+  <si>
+    <t>青苹果柠檬果冻杯</t>
+  </si>
+  <si>
+    <t>Dishes_AppleJellyCup</t>
+  </si>
+  <si>
+    <t>3003,3009,3010,3011</t>
+  </si>
+  <si>
+    <t>4003,4005</t>
+  </si>
+  <si>
+    <t>烤鱼</t>
+  </si>
+  <si>
+    <t>Dishes_ToastedFish</t>
+  </si>
+  <si>
+    <t>3003,3006,3007,3019</t>
+  </si>
+  <si>
+    <t>番茄肉酱面</t>
+  </si>
+  <si>
+    <t>Dishes_TomatoMeatNoodles</t>
+  </si>
+  <si>
+    <t>2014,3022</t>
+  </si>
+  <si>
+    <t>番茄肉酱</t>
+  </si>
+  <si>
+    <t>3004,3012,3020</t>
+  </si>
+  <si>
+    <t>4002,4004,4005</t>
+  </si>
+  <si>
+    <t>蛋炒饭</t>
+  </si>
+  <si>
+    <t>Dishes_EggFriedRice</t>
+  </si>
+  <si>
+    <t>3007,3013,3018,3023</t>
+  </si>
+  <si>
+    <t>4004</t>
+  </si>
+  <si>
+    <t>水晶山楂糕</t>
+  </si>
+  <si>
+    <t>Dishes_HawthornJelly</t>
+  </si>
+  <si>
+    <t>3011,3014</t>
+  </si>
+  <si>
+    <t>牛肉滑蛋饭</t>
+  </si>
+  <si>
+    <t>Dishes_RiceWithSlicedBeefEggs</t>
+  </si>
+  <si>
+    <t>3013,3017,3023</t>
+  </si>
+  <si>
+    <t>4004,4006</t>
+  </si>
+  <si>
+    <t>番茄酿肉</t>
+  </si>
+  <si>
+    <t>Dishes_Tomato StuffedWithMeat</t>
+  </si>
+  <si>
+    <t>‘3002,3004,3012,3020,3023</t>
+  </si>
+  <si>
+    <t>芝士肉酱土豆饼</t>
+  </si>
+  <si>
+    <t>Dishes_CheesePotatoPancake</t>
+  </si>
+  <si>
+    <t>3008,3015,3017,1023</t>
+  </si>
+  <si>
+    <t>青菜鸡蛋面</t>
+  </si>
+  <si>
+    <t>Dishes_VeggieAndEggNoodles</t>
+  </si>
+  <si>
+    <t>‘3007,3016,3022,3023</t>
+  </si>
+  <si>
+    <t>沙拉</t>
+  </si>
+  <si>
+    <t>Dishes_Salad</t>
+  </si>
+  <si>
+    <t>‘3004,3016,3018,3023,</t>
+  </si>
+  <si>
+    <t>小鸡滑蛋盖浇饭</t>
+  </si>
+  <si>
+    <t>Dishes_Oyakodon</t>
+  </si>
+  <si>
+    <t>3008,3010,3013,3015,3017,3023</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -134,30 +686,328 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -206,7 +1056,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
@@ -241,7 +1091,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
@@ -415,108 +1265,689 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:J26"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.85"/>
   <cols>
-    <col min="2" max="2" width="10.796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.1328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.86328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.9296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.06640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7964601769912" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.5132743362832" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.0884955752212" style="1" customWidth="1"/>
+    <col min="5" max="5" width="27.9469026548673" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.0619469026549" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.0088495575221" style="1" customWidth="1"/>
+    <col min="8" max="8" width="14.283185840708" style="1" customWidth="1"/>
+    <col min="9" max="9" width="16.929203539823" style="1" customWidth="1"/>
+    <col min="10" max="10" width="14.070796460177" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A2" s="2" t="s">
+      <c r="G2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J2" s="3"/>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="J3" s="3"/>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J4" s="3"/>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="B5" s="1">
+        <v>2001</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="1">
+        <v>5004</v>
+      </c>
+      <c r="H5" s="1">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="I5" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="B6" s="1">
+        <v>2002</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="1">
+        <v>4004</v>
+      </c>
+      <c r="G6" s="1">
+        <v>5003</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="B7" s="1">
+        <v>2003</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" s="1">
+        <v>5004</v>
+      </c>
+      <c r="H7" s="1">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="B8" s="1">
+        <v>2004</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="1">
+        <v>5004</v>
+      </c>
+      <c r="H8" s="1">
         <v>2</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="I8" s="1">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="B9" s="1">
+        <v>2005</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9" s="1">
+        <v>5001</v>
+      </c>
+      <c r="H9" s="1">
+        <v>2</v>
+      </c>
+      <c r="I9" s="1">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="B10" s="1">
+        <v>2006</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" s="1">
+        <v>5001</v>
+      </c>
+      <c r="H10" s="1">
+        <v>2</v>
+      </c>
+      <c r="I10" s="1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="B11" s="1">
+        <v>2007</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" s="1">
+        <v>5004</v>
+      </c>
+      <c r="H11" s="1">
+        <v>2</v>
+      </c>
+      <c r="I11" s="1">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="B12" s="1">
+        <v>2008</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="G12" s="1">
+        <v>5005</v>
+      </c>
+      <c r="H12" s="1">
         <v>3</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="I12" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="B13" s="1">
+        <v>2009</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="G13" s="1">
+        <v>5005</v>
+      </c>
+      <c r="H13" s="1">
+        <v>3</v>
+      </c>
+      <c r="I13" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="B14" s="1">
+        <v>2010</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="G14" s="1">
+        <v>5001</v>
+      </c>
+      <c r="H14" s="1">
+        <v>3</v>
+      </c>
+      <c r="I14" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="B15" s="1">
+        <v>2011</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G15" s="1">
+        <v>5004</v>
+      </c>
+      <c r="H15" s="1">
         <v>4</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="I15" s="1">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="B16" s="1">
+        <v>2012</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="G16" s="1">
+        <v>5005</v>
+      </c>
+      <c r="H16" s="1">
+        <v>4</v>
+      </c>
+      <c r="I16" s="1">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9">
+      <c r="B17" s="1">
+        <v>2013</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G17" s="1">
+        <v>5001</v>
+      </c>
+      <c r="H17" s="1">
+        <v>4</v>
+      </c>
+      <c r="I17" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9">
+      <c r="B18" s="1">
+        <v>2014</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="G18" s="1">
+        <v>5001</v>
+      </c>
+      <c r="H18" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9">
+      <c r="B19" s="1">
+        <v>2015</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="G19" s="1">
+        <v>5001</v>
+      </c>
+      <c r="H19" s="1">
         <v>5</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A4" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>17</v>
+      <c r="I19" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9">
+      <c r="B20" s="1">
+        <v>2016</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G20" s="1">
+        <v>5004</v>
+      </c>
+      <c r="H20" s="1">
+        <v>5</v>
+      </c>
+      <c r="I20" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9">
+      <c r="B21" s="1">
+        <v>2017</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="G21" s="1">
+        <v>5001</v>
+      </c>
+      <c r="H21" s="1">
+        <v>5</v>
+      </c>
+      <c r="I21" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9">
+      <c r="B22" s="1">
+        <v>2018</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="G22" s="1">
+        <v>5005</v>
+      </c>
+      <c r="H22" s="1">
+        <v>5</v>
+      </c>
+      <c r="I22" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9">
+      <c r="B23" s="1">
+        <v>2019</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G23" s="1">
+        <v>5001</v>
+      </c>
+      <c r="H23" s="1">
+        <v>6</v>
+      </c>
+      <c r="I23" s="1">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9">
+      <c r="B24" s="1">
+        <v>2020</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G24" s="1">
+        <v>5004</v>
+      </c>
+      <c r="H24" s="1">
+        <v>6</v>
+      </c>
+      <c r="I24" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9">
+      <c r="B25" s="1">
+        <v>2021</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="G25" s="1">
+        <v>5001</v>
+      </c>
+      <c r="H25" s="1">
+        <v>6</v>
+      </c>
+      <c r="I25" s="1">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9">
+      <c r="B26" s="1">
+        <v>2022</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="G26" s="1">
+        <v>5004</v>
+      </c>
+      <c r="H26" s="1">
+        <v>6</v>
+      </c>
+      <c r="I26" s="1">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/Assets/LingBoCanteen/1_Datatables/Excel/Dish.xlsx
+++ b/Assets/LingBoCanteen/1_Datatables/Excel/Dish.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="98">
   <si>
     <t>#</t>
   </si>
@@ -53,6 +53,12 @@
     <t>PotList</t>
   </si>
   <si>
+    <t>RecipeAsset</t>
+  </si>
+  <si>
+    <t>Weight</t>
+  </si>
+  <si>
     <t>EarnMoney</t>
   </si>
   <si>
@@ -81,6 +87,9 @@
   </si>
   <si>
     <t>所需锅</t>
+  </si>
+  <si>
+    <t>关联配方资源</t>
   </si>
   <si>
     <t>需求抽取权重</t>
@@ -324,14 +333,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -787,161 +789,158 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1271,7 +1270,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.85"/>
   <cols>
     <col min="2" max="2" width="10.7964601769912" style="1" customWidth="1"/>
@@ -1280,147 +1279,157 @@
     <col min="5" max="5" width="27.9469026548673" style="1" customWidth="1"/>
     <col min="6" max="6" width="17.0619469026549" style="1" customWidth="1"/>
     <col min="7" max="7" width="13.0088495575221" style="1" customWidth="1"/>
-    <col min="8" max="8" width="14.283185840708" style="1" customWidth="1"/>
-    <col min="9" max="9" width="16.929203539823" style="1" customWidth="1"/>
-    <col min="10" max="10" width="14.070796460177" customWidth="1"/>
+    <col min="8" max="8" width="13.4159292035398" style="1" customWidth="1"/>
+    <col min="9" max="9" width="14.283185840708" style="1" customWidth="1"/>
+    <col min="10" max="10" width="16.929203539823" style="1" customWidth="1"/>
+    <col min="11" max="11" width="14.070796460177" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="3" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3" t="s">
+      <c r="H2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="3"/>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="3" t="s">
+      <c r="I2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="1"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="C3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="J3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="J3" s="3"/>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="3" t="s">
+      <c r="K3" s="1"/>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="B4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="C4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="D4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="E4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="F4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="G4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="3"/>
-    </row>
-    <row r="5" spans="1:10">
+      <c r="H4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K4" s="1"/>
+    </row>
+    <row r="5" spans="1:11">
       <c r="B5" s="1">
         <v>2001</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="G5" s="1">
         <v>5004</v>
       </c>
-      <c r="H5" s="1">
+      <c r="I5" s="1">
         <v>1</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:11">
       <c r="B6" s="1">
         <v>2002</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>26</v>
+        <v>28</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="F6" s="1">
         <v>4004</v>
@@ -1428,521 +1437,521 @@
       <c r="G6" s="1">
         <v>5003</v>
       </c>
-      <c r="H6" s="1">
+      <c r="I6" s="1">
         <v>1</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6" s="1">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:11">
       <c r="B7" s="1">
         <v>2003</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>23</v>
+        <v>31</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="G7" s="1">
         <v>5004</v>
       </c>
-      <c r="H7" s="1">
+      <c r="I7" s="1">
         <v>1</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:11">
       <c r="B8" s="1">
         <v>2004</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="G8" s="1">
         <v>5004</v>
       </c>
-      <c r="H8" s="1">
+      <c r="I8" s="1">
         <v>2</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:11">
       <c r="B9" s="1">
         <v>2005</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>36</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>33</v>
       </c>
       <c r="G9" s="1">
         <v>5001</v>
       </c>
-      <c r="H9" s="1">
+      <c r="I9" s="1">
         <v>2</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:11">
       <c r="B10" s="1">
         <v>2006</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>33</v>
+        <v>41</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>36</v>
       </c>
       <c r="G10" s="1">
         <v>5001</v>
       </c>
-      <c r="H10" s="1">
+      <c r="I10" s="1">
         <v>2</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10" s="1">
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:11">
       <c r="B11" s="1">
         <v>2007</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>46</v>
       </c>
       <c r="G11" s="1">
         <v>5004</v>
       </c>
-      <c r="H11" s="1">
+      <c r="I11" s="1">
         <v>2</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J11" s="1">
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:11">
       <c r="B12" s="1">
         <v>2008</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>50</v>
       </c>
       <c r="G12" s="1">
         <v>5005</v>
       </c>
-      <c r="H12" s="1">
+      <c r="I12" s="1">
         <v>3</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12" s="1">
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:11">
       <c r="B13" s="1">
         <v>2009</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="G13" s="1">
         <v>5005</v>
       </c>
-      <c r="H13" s="1">
+      <c r="I13" s="1">
         <v>3</v>
       </c>
-      <c r="I13" s="1">
+      <c r="J13" s="1">
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:11">
       <c r="B14" s="1">
         <v>2010</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="G14" s="1">
         <v>5001</v>
       </c>
-      <c r="H14" s="1">
+      <c r="I14" s="1">
         <v>3</v>
       </c>
-      <c r="I14" s="1">
+      <c r="J14" s="1">
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:11">
       <c r="B15" s="1">
         <v>2011</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>62</v>
       </c>
       <c r="G15" s="1">
         <v>5004</v>
       </c>
-      <c r="H15" s="1">
+      <c r="I15" s="1">
         <v>4</v>
       </c>
-      <c r="I15" s="1">
+      <c r="J15" s="1">
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:11">
       <c r="B16" s="1">
         <v>2012</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>33</v>
+        <v>64</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="G16" s="1">
         <v>5005</v>
       </c>
-      <c r="H16" s="1">
+      <c r="I16" s="1">
         <v>4</v>
       </c>
-      <c r="I16" s="1">
+      <c r="J16" s="1">
         <v>34</v>
       </c>
     </row>
-    <row r="17" spans="2:9">
+    <row r="17" spans="2:10">
       <c r="B17" s="1">
         <v>2013</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>68</v>
       </c>
       <c r="G17" s="1">
         <v>5001</v>
       </c>
-      <c r="H17" s="1">
+      <c r="I17" s="1">
         <v>4</v>
       </c>
-      <c r="I17" s="1">
+      <c r="J17" s="1">
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="2:9">
+    <row r="18" spans="2:10">
       <c r="B18" s="1">
         <v>2014</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>71</v>
       </c>
       <c r="G18" s="1">
         <v>5001</v>
       </c>
-      <c r="H18" s="1">
+      <c r="I18" s="1">
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="2:9">
+    <row r="19" spans="2:10">
       <c r="B19" s="1">
         <v>2015</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>75</v>
       </c>
       <c r="G19" s="1">
         <v>5001</v>
       </c>
-      <c r="H19" s="1">
+      <c r="I19" s="1">
         <v>5</v>
       </c>
-      <c r="I19" s="1">
+      <c r="J19" s="1">
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="2:9">
+    <row r="20" spans="2:10">
       <c r="B20" s="1">
         <v>2016</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>23</v>
+        <v>77</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="G20" s="1">
-        <v>5004</v>
-      </c>
-      <c r="H20" s="1">
+        <v>5002</v>
+      </c>
+      <c r="I20" s="1">
         <v>5</v>
       </c>
-      <c r="I20" s="1">
+      <c r="J20" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="2:9">
+    <row r="21" spans="2:10">
       <c r="B21" s="1">
         <v>2017</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="G21" s="1">
         <v>5001</v>
       </c>
-      <c r="H21" s="1">
+      <c r="I21" s="1">
         <v>5</v>
       </c>
-      <c r="I21" s="1">
+      <c r="J21" s="1">
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="2:9">
+    <row r="22" spans="2:10">
       <c r="B22" s="1">
         <v>2018</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E22" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F22" s="5" t="s">
         <v>82</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>79</v>
       </c>
       <c r="G22" s="1">
         <v>5005</v>
       </c>
-      <c r="H22" s="1">
+      <c r="I22" s="1">
         <v>5</v>
       </c>
-      <c r="I22" s="1">
+      <c r="J22" s="1">
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="2:9">
+    <row r="23" spans="2:10">
       <c r="B23" s="1">
         <v>2019</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>33</v>
+        <v>87</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>36</v>
       </c>
       <c r="G23" s="1">
         <v>5001</v>
       </c>
-      <c r="H23" s="1">
+      <c r="I23" s="1">
         <v>6</v>
       </c>
-      <c r="I23" s="1">
+      <c r="J23" s="1">
         <v>57</v>
       </c>
     </row>
-    <row r="24" spans="2:9">
+    <row r="24" spans="2:10">
       <c r="B24" s="1">
         <v>2020</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>33</v>
+        <v>91</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>36</v>
       </c>
       <c r="G24" s="1">
         <v>5004</v>
       </c>
-      <c r="H24" s="1">
+      <c r="I24" s="1">
         <v>6</v>
       </c>
-      <c r="I24" s="1">
+      <c r="J24" s="1">
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="2:9">
+    <row r="25" spans="2:10">
       <c r="B25" s="1">
         <v>2021</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>33</v>
+        <v>94</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>36</v>
       </c>
       <c r="G25" s="1">
         <v>5001</v>
       </c>
-      <c r="H25" s="1">
+      <c r="I25" s="1">
         <v>6</v>
       </c>
-      <c r="I25" s="1">
+      <c r="J25" s="1">
         <v>82</v>
       </c>
     </row>
-    <row r="26" spans="2:9">
+    <row r="26" spans="2:10">
       <c r="B26" s="1">
         <v>2022</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>51</v>
+        <v>96</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="G26" s="1">
         <v>5004</v>
       </c>
-      <c r="H26" s="1">
+      <c r="I26" s="1">
         <v>6</v>
       </c>
-      <c r="I26" s="1">
+      <c r="J26" s="1">
         <v>72</v>
       </c>
     </row>
